--- a/AAII_Financials/Yearly/AC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AC_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/AC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
   <si>
     <t>AC</t>
   </si>
@@ -656,112 +656,118 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E8" s="3">
         <v>15200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>19000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>22200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>22800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>26900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>31200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>22800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21500</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -801,9 +807,12 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -843,9 +852,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,9 +961,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -976,20 +995,23 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M14" s="3">
         <v>100</v>
       </c>
       <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E17" s="3">
         <v>26500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>40000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>31500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>35500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>36300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>47300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>43500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>37200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>31000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>35000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>34300</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-19100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-20400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-12200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-14300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-14600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-12700</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,218 +1179,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>64300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-49000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>42500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>70700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-55100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>26900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>27200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>13000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>11000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>56900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>25500</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-59900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>82000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>30100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>57500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-68600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>15000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>42300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12700</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>500</v>
+      </c>
+      <c r="E22" s="3">
         <v>200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>300</v>
-      </c>
-      <c r="F22" s="3">
-        <v>200</v>
       </c>
       <c r="G22" s="3">
         <v>200</v>
       </c>
       <c r="H22" s="3">
+        <v>200</v>
+      </c>
+      <c r="I22" s="3">
         <v>300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1400</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1900</v>
       </c>
       <c r="N22" s="3">
         <v>1900</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-60500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>81300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>29900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>57200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-68900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>14300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>40400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>10800</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-14900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>17700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-11500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>13200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3100</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-45500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>63600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>20500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>44600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-57400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>27200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7700</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-48900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>59200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>19400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>41100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-58100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>26800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7500</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,33 +1581,36 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-600</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-1900</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3">
         <v>1700</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-64300</v>
+      </c>
+      <c r="E32" s="3">
         <v>49000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-42500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-70700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>55100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-26900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-27200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-13000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-11000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-56900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-25500</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-48900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>59200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>18800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>39200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-58100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>26800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7500</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-48900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>59200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>18800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>39200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-58100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>26800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7500</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,50 +1987,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>317500</v>
+      </c>
+      <c r="E41" s="3">
         <v>218500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>319000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>39500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>348600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>409600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>293100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>314100</v>
-      </c>
-      <c r="K41" s="3">
-        <v>205800</v>
       </c>
       <c r="L41" s="3">
         <v>205800</v>
       </c>
       <c r="M41" s="3">
+        <v>205800</v>
+      </c>
+      <c r="N41" s="3">
         <v>199500</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1985,51 +2074,57 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E43" s="3">
         <v>15900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>50800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>32000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>33700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>28800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>40600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>22400</v>
-      </c>
-      <c r="K43" s="3">
-        <v>61400</v>
       </c>
       <c r="L43" s="3">
         <v>61400</v>
       </c>
       <c r="M43" s="3">
+        <v>61400</v>
+      </c>
+      <c r="N43" s="3">
         <v>54100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2069,9 +2164,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2111,9 +2209,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2153,69 +2254,75 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>564800</v>
+      </c>
+      <c r="E47" s="3">
         <v>671100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>808300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1068700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>609100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>491700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>659800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>605200</v>
-      </c>
-      <c r="K47" s="3">
-        <v>564800</v>
       </c>
       <c r="L47" s="3">
         <v>564800</v>
       </c>
       <c r="M47" s="3">
+        <v>564800</v>
+      </c>
+      <c r="N47" s="3">
         <v>329000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E48" s="3">
         <v>16900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6600</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2228,8 +2335,8 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -2237,9 +2344,12 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2259,13 +2369,13 @@
         <v>3500</v>
       </c>
       <c r="I49" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="J49" s="3">
         <v>3400</v>
       </c>
       <c r="K49" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="L49" s="3">
         <v>3300</v>
@@ -2273,15 +2383,18 @@
       <c r="M49" s="3">
         <v>3300</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
+      <c r="N49" s="3">
+        <v>3300</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,30 +2479,33 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
         <v>2200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9400</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2402,12 +2521,15 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>943800</v>
+      </c>
+      <c r="E54" s="3">
         <v>927700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1203300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1174500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1010900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>954400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1006900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>952600</v>
-      </c>
-      <c r="K54" s="3">
-        <v>836700</v>
       </c>
       <c r="L54" s="3">
         <v>836700</v>
       </c>
       <c r="M54" s="3">
+        <v>836700</v>
+      </c>
+      <c r="N54" s="3">
         <v>588700</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,134 +2655,144 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E57" s="3">
         <v>7800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2400</v>
-      </c>
-      <c r="K57" s="3">
-        <v>50600</v>
       </c>
       <c r="L57" s="3">
         <v>50600</v>
       </c>
       <c r="M57" s="3">
+        <v>50600</v>
+      </c>
+      <c r="N57" s="3">
         <v>10000</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E58" s="3">
         <v>2900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>16300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9900</v>
-      </c>
-      <c r="K58" s="3">
-        <v>9500</v>
       </c>
       <c r="L58" s="3">
         <v>9500</v>
       </c>
       <c r="M58" s="3">
+        <v>9500</v>
+      </c>
+      <c r="N58" s="3">
         <v>6200</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E59" s="3">
         <v>16600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>38000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>42300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>31800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>23300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>23500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>62000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>18100</v>
       </c>
       <c r="L59" s="3">
         <v>18100</v>
       </c>
       <c r="M59" s="3">
+        <v>18100</v>
+      </c>
+      <c r="N59" s="3">
         <v>69100</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2693,9 +2832,12 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2721,23 +2863,26 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3">
         <v>1100</v>
       </c>
       <c r="M61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N61" s="3">
         <v>1400</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2777,9 +2922,12 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E66" s="3">
         <v>37500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>266200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>275600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>114500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>88200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>88800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>78600</v>
-      </c>
-      <c r="K66" s="3">
-        <v>87600</v>
       </c>
       <c r="L66" s="3">
         <v>87600</v>
       </c>
       <c r="M66" s="3">
+        <v>87600</v>
+      </c>
+      <c r="N66" s="3">
         <v>93300</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,41 +3301,44 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E72" s="3">
         <v>15100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>68400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>13600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-39900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>13800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7300</v>
-      </c>
-      <c r="K72" s="3">
-        <v>2100</v>
       </c>
       <c r="L72" s="3">
         <v>2100</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
+      <c r="M72" s="3">
+        <v>2100</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
@@ -3173,9 +3346,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>907000</v>
+      </c>
+      <c r="E76" s="3">
         <v>890200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>937100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>898900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>896400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>866200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>918100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>874000</v>
-      </c>
-      <c r="K76" s="3">
-        <v>749200</v>
       </c>
       <c r="L76" s="3">
         <v>749200</v>
       </c>
       <c r="M76" s="3">
+        <v>749200</v>
+      </c>
+      <c r="N76" s="3">
         <v>495400</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-48900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>59200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>18800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>39200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-58100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>26800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7500</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,23 +3688,24 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>400</v>
+      </c>
+      <c r="E83" s="3">
         <v>300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
         <v>0</v>
       </c>
@@ -3517,24 +3715,27 @@
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>145100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-70600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>238200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-279400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-44300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>77000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-67600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6600</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-58600</v>
       </c>
       <c r="L89" s="3">
         <v>-58600</v>
       </c>
       <c r="M89" s="3">
+        <v>-58600</v>
+      </c>
+      <c r="N89" s="3">
         <v>40800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2800</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,26 +4022,27 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-11100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6500</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3838,15 +4058,18 @@
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E94" s="3">
         <v>400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>65300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-174100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>4700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4100</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>29400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1900</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,35 +4221,36 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-4400</v>
+        <v>-4300</v>
       </c>
       <c r="E96" s="3">
         <v>-4400</v>
       </c>
       <c r="F96" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="G96" s="3">
         <v>-6700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-4500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-4700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-4800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-2500</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,51 +4398,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-37200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-14400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>150900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-11600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>34700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>65400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>105900</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>-50500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-88400</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4225,14 +4473,14 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4240,49 +4488,55 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>125800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-107300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>289100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-302500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-61000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>116500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-21000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>108300</v>
-      </c>
-      <c r="K102" s="3">
-        <v>86000</v>
       </c>
       <c r="L102" s="3">
         <v>86000</v>
       </c>
       <c r="M102" s="3">
+        <v>86000</v>
+      </c>
+      <c r="N102" s="3">
         <v>19700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-89300</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
   <si>
     <t>AC</t>
   </si>
@@ -771,26 +771,26 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>18900</v>
+      </c>
+      <c r="F9" s="3">
+        <v>24500</v>
+      </c>
+      <c r="G9" s="3">
+        <v>19400</v>
+      </c>
+      <c r="H9" s="3">
+        <v>23800</v>
+      </c>
+      <c r="I9" s="3">
+        <v>26600</v>
+      </c>
+      <c r="J9" s="3">
+        <v>36500</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -816,26 +816,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-9600</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -971,25 +971,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-43000</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>56500</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-93400</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-36900</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>-60800</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>65200</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-20600</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1016,16 +1016,16 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>64300</v>
+        <v>4000</v>
       </c>
       <c r="E20" s="3">
-        <v>-49000</v>
+        <v>3100</v>
       </c>
       <c r="F20" s="3">
-        <v>100700</v>
+        <v>4800</v>
       </c>
       <c r="G20" s="3">
-        <v>42500</v>
+        <v>3000</v>
       </c>
       <c r="H20" s="3">
-        <v>70700</v>
+        <v>3300</v>
       </c>
       <c r="I20" s="3">
-        <v>-55100</v>
+        <v>3300</v>
       </c>
       <c r="J20" s="3">
-        <v>26900</v>
+        <v>4200</v>
       </c>
       <c r="K20" s="3">
         <v>27200</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>47700</v>
+        <v>-20600</v>
       </c>
       <c r="E21" s="3">
-        <v>-59900</v>
+        <v>-14000</v>
       </c>
       <c r="F21" s="3">
-        <v>82000</v>
+        <v>-23500</v>
       </c>
       <c r="G21" s="3">
-        <v>30100</v>
+        <v>-15400</v>
       </c>
       <c r="H21" s="3">
-        <v>57500</v>
+        <v>-16500</v>
       </c>
       <c r="I21" s="3">
-        <v>-68600</v>
+        <v>-16800</v>
       </c>
       <c r="J21" s="3">
-        <v>6500</v>
+        <v>-24600</v>
       </c>
       <c r="K21" s="3">
         <v>15000</v>
@@ -1384,7 +1384,7 @@
         <v>-11500</v>
       </c>
       <c r="J24" s="3">
-        <v>-700</v>
+        <v>-2400</v>
       </c>
       <c r="K24" s="3">
         <v>3900</v>
@@ -1474,7 +1474,7 @@
         <v>-57400</v>
       </c>
       <c r="J26" s="3">
-        <v>7000</v>
+        <v>8700</v>
       </c>
       <c r="K26" s="3">
         <v>10500</v>
@@ -1510,16 +1510,16 @@
         <v>59200</v>
       </c>
       <c r="G27" s="3">
-        <v>19400</v>
+        <v>18800</v>
       </c>
       <c r="H27" s="3">
-        <v>41100</v>
+        <v>39200</v>
       </c>
       <c r="I27" s="3">
         <v>-58100</v>
       </c>
       <c r="J27" s="3">
-        <v>7100</v>
+        <v>8800</v>
       </c>
       <c r="K27" s="3">
         <v>10200</v>
@@ -1590,11 +1590,11 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -1605,11 +1605,11 @@
       <c r="H29" s="3">
         <v>-1900</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-64300</v>
+        <v>-4000</v>
       </c>
       <c r="E32" s="3">
-        <v>49000</v>
+        <v>-3100</v>
       </c>
       <c r="F32" s="3">
-        <v>-100700</v>
+        <v>-4800</v>
       </c>
       <c r="G32" s="3">
-        <v>-42500</v>
+        <v>-3000</v>
       </c>
       <c r="H32" s="3">
-        <v>-70700</v>
+        <v>-3300</v>
       </c>
       <c r="I32" s="3">
-        <v>55100</v>
+        <v>-3300</v>
       </c>
       <c r="J32" s="3">
-        <v>-26900</v>
+        <v>-4200</v>
       </c>
       <c r="K32" s="3">
         <v>-27200</v>
@@ -2006,7 +2006,7 @@
         <v>39500</v>
       </c>
       <c r="H41" s="3">
-        <v>348600</v>
+        <v>342000</v>
       </c>
       <c r="I41" s="3">
         <v>409600</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>89200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>186000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>61000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>344500</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>29000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>11700</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>362600</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>35000</v>
+        <v>36500</v>
       </c>
       <c r="E43" s="3">
-        <v>15900</v>
+        <v>25900</v>
       </c>
       <c r="F43" s="3">
-        <v>50800</v>
+        <v>46300</v>
       </c>
       <c r="G43" s="3">
-        <v>32000</v>
+        <v>36800</v>
       </c>
       <c r="H43" s="3">
-        <v>33700</v>
+        <v>37000</v>
       </c>
       <c r="I43" s="3">
-        <v>28800</v>
+        <v>29900</v>
       </c>
       <c r="J43" s="3">
-        <v>40600</v>
+        <v>56300</v>
       </c>
       <c r="K43" s="3">
         <v>22400</v>
@@ -2128,26 +2128,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2173,26 +2173,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>451000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>433200</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>435900</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>420700</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>416500</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>452100</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>712200</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>564800</v>
+        <v>466300</v>
       </c>
       <c r="E47" s="3">
-        <v>671100</v>
+        <v>472300</v>
       </c>
       <c r="F47" s="3">
-        <v>808300</v>
+        <v>567200</v>
       </c>
       <c r="G47" s="3">
-        <v>1068700</v>
+        <v>544500</v>
       </c>
       <c r="H47" s="3">
-        <v>609100</v>
+        <v>575700</v>
       </c>
       <c r="I47" s="3">
-        <v>491700</v>
+        <v>478700</v>
       </c>
       <c r="J47" s="3">
-        <v>659800</v>
+        <v>281500</v>
       </c>
       <c r="K47" s="3">
         <v>605200</v>
@@ -2488,26 +2488,26 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1800</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>179600</v>
       </c>
       <c r="G52" s="3">
-        <v>2200</v>
+        <v>186100</v>
       </c>
       <c r="H52" s="3">
-        <v>2000</v>
+        <v>6700</v>
       </c>
       <c r="I52" s="3">
-        <v>9400</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>10800</v>
+      </c>
+      <c r="J52" s="3">
+        <v>9800</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2661,26 +2661,26 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>4500</v>
-      </c>
-      <c r="E57" s="3">
-        <v>7800</v>
-      </c>
-      <c r="F57" s="3">
-        <v>9300</v>
-      </c>
-      <c r="G57" s="3">
-        <v>6500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>14900</v>
-      </c>
-      <c r="I57" s="3">
-        <v>5500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>13300</v>
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3">
         <v>2400</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5900</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>12900</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>17600</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>16300</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>9900</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>20300</v>
+        <v>5900</v>
       </c>
       <c r="E59" s="3">
-        <v>16600</v>
+        <v>2900</v>
       </c>
       <c r="F59" s="3">
-        <v>38000</v>
+        <v>13800</v>
       </c>
       <c r="G59" s="3">
-        <v>42300</v>
+        <v>27300</v>
       </c>
       <c r="H59" s="3">
-        <v>31800</v>
+        <v>24400</v>
       </c>
       <c r="I59" s="3">
-        <v>23300</v>
+        <v>15500</v>
       </c>
       <c r="J59" s="3">
-        <v>23500</v>
+        <v>13600</v>
       </c>
       <c r="K59" s="3">
         <v>62000</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>12400</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>25200</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>37400</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>41100</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>23200</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>14900</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>32600</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>28900</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>15200</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>13200</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>36800</v>
+        <v>30700</v>
       </c>
       <c r="E66" s="3">
-        <v>37500</v>
+        <v>27300</v>
       </c>
       <c r="F66" s="3">
-        <v>266200</v>
+        <v>65500</v>
       </c>
       <c r="G66" s="3">
-        <v>275600</v>
+        <v>66300</v>
       </c>
       <c r="H66" s="3">
-        <v>114500</v>
+        <v>63100</v>
       </c>
       <c r="I66" s="3">
-        <v>88200</v>
+        <v>38400</v>
       </c>
       <c r="J66" s="3">
-        <v>88800</v>
+        <v>42500</v>
       </c>
       <c r="K66" s="3">
         <v>78600</v>
@@ -4034,8 +4034,8 @@
       <c r="E91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G91" s="3">
         <v>-11100</v>
@@ -4228,25 +4228,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-4300</v>
+        <v>4300</v>
       </c>
       <c r="E96" s="3">
-        <v>-4400</v>
+        <v>4400</v>
       </c>
       <c r="F96" s="3">
-        <v>-4400</v>
+        <v>4400</v>
       </c>
       <c r="G96" s="3">
-        <v>-6700</v>
+        <v>6700</v>
       </c>
       <c r="H96" s="3">
-        <v>-4500</v>
+        <v>4500</v>
       </c>
       <c r="I96" s="3">
-        <v>-4700</v>
+        <v>4700</v>
       </c>
       <c r="J96" s="3">
-        <v>-4800</v>
+        <v>4800</v>
       </c>
       <c r="K96" s="3">
         <v>-2500</v>
@@ -4452,26 +4452,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>-61000</v>
       </c>
       <c r="I102" s="3">
-        <v>116500</v>
+        <v>116400</v>
       </c>
       <c r="J102" s="3">
         <v>-21000</v>

--- a/AAII_Financials/Yearly/AC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
   <si>
     <t>AC</t>
   </si>
@@ -656,145 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E8" s="3">
         <v>12700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>19000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>22200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>22800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>26900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>31200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>22800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>21500</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E9" s="3">
         <v>17200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>18900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>24500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>19400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>23800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>36500</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,36 +816,39 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-4600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-3700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-3500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-1600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-3800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-9600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,9 +864,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,8 +887,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,54 +980,60 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-42800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-43000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>56500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-93400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-36900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-60800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>65200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-20600</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N14" s="3">
         <v>100</v>
       </c>
       <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1019,17 +1041,17 @@
         <v>400</v>
       </c>
       <c r="E15" s="3">
+        <v>400</v>
+      </c>
+      <c r="F15" s="3">
         <v>300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
       <c r="I15" s="3">
         <v>0</v>
       </c>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E17" s="3">
         <v>29600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>26500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>40000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>31500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>35500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>36300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>47300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>43500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>37200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>31000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>35000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>34300</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-16900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-11300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-19100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-12500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-20400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-12200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-14600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-12700</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,233 +1212,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E20" s="3">
         <v>4000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>3300</v>
       </c>
       <c r="I20" s="3">
         <v>3300</v>
       </c>
       <c r="J20" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K20" s="3">
         <v>4200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>27200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>13000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>11000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>56900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>25500</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-20600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-14000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-23500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-15400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-16500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-24600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>15000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>42300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12700</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>300</v>
+      </c>
+      <c r="E22" s="3">
         <v>500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>300</v>
-      </c>
-      <c r="G22" s="3">
-        <v>200</v>
       </c>
       <c r="H22" s="3">
         <v>200</v>
       </c>
       <c r="I22" s="3">
+        <v>200</v>
+      </c>
+      <c r="J22" s="3">
         <v>300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1400</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1900</v>
       </c>
       <c r="O22" s="3">
         <v>1900</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E23" s="3">
         <v>46900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-60500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>81300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>29900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>57200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-68900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>14300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>40400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>10800</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E24" s="3">
         <v>9100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-14900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>17700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>12600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-11500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>13200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3100</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E26" s="3">
         <v>37700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-45500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>63600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>20500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>44600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-57400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>27200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7700</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E27" s="3">
         <v>37500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-48900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>59200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>18800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>39200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-58100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>26800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7500</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1600,19 +1660,19 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-600</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-1900</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>3</v>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-3300</v>
       </c>
       <c r="I32" s="3">
         <v>-3300</v>
       </c>
       <c r="J32" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-4200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-27200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-13000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-11000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-56900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-25500</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E33" s="3">
         <v>37500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-48900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>59200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>18800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>39200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-58100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>26800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7500</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E35" s="3">
         <v>37500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-48900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>59200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>18800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>39200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-58100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>26800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7500</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,80 +2073,84 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>299600</v>
+      </c>
+      <c r="E41" s="3">
         <v>317500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>218500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>319000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>39500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>342000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>409600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>293100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>314100</v>
-      </c>
-      <c r="L41" s="3">
-        <v>205800</v>
       </c>
       <c r="M41" s="3">
         <v>205800</v>
       </c>
       <c r="N41" s="3">
+        <v>205800</v>
+      </c>
+      <c r="O41" s="3">
         <v>199500</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>68300</v>
+      </c>
+      <c r="E42" s="3">
         <v>89200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>186000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>61000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>344500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>29000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>362600</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2077,54 +2166,60 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E43" s="3">
         <v>36500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>46300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>36800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>37000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>29900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>56300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>22400</v>
-      </c>
-      <c r="L43" s="3">
-        <v>61400</v>
       </c>
       <c r="M43" s="3">
         <v>61400</v>
       </c>
       <c r="N43" s="3">
+        <v>61400</v>
+      </c>
+      <c r="O43" s="3">
         <v>54100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2149,8 +2244,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2167,9 +2262,12 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2185,17 +2283,17 @@
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>8500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>700</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -2212,36 +2310,39 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>406300</v>
+      </c>
+      <c r="E46" s="3">
         <v>451000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>433200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>435900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>420700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>416500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>452100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>712200</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2257,75 +2358,81 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>504500</v>
+      </c>
+      <c r="E47" s="3">
         <v>466300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>472300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>567200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>544500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>575700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>478700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>281500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>605200</v>
-      </c>
-      <c r="L47" s="3">
-        <v>564800</v>
       </c>
       <c r="M47" s="3">
         <v>564800</v>
       </c>
       <c r="N47" s="3">
+        <v>564800</v>
+      </c>
+      <c r="O47" s="3">
         <v>329000</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E48" s="3">
         <v>16500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>16900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>17500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6600</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2338,8 +2445,8 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -2347,9 +2454,12 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2372,13 +2482,13 @@
         <v>3500</v>
       </c>
       <c r="J49" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="K49" s="3">
         <v>3400</v>
       </c>
       <c r="L49" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="M49" s="3">
         <v>3300</v>
@@ -2386,15 +2496,18 @@
       <c r="N49" s="3">
         <v>3300</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
+      <c r="O49" s="3">
+        <v>3300</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,36 +2598,39 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E52" s="3">
         <v>6500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>179600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>186100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9800</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2524,12 +2643,15 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>935300</v>
+      </c>
+      <c r="E54" s="3">
         <v>943800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>927700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1203300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1174500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1010900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>954400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1006900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>952600</v>
-      </c>
-      <c r="L54" s="3">
-        <v>836700</v>
       </c>
       <c r="M54" s="3">
         <v>836700</v>
       </c>
       <c r="N54" s="3">
+        <v>836700</v>
+      </c>
+      <c r="O54" s="3">
         <v>588700</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,8 +2785,9 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2682,27 +2812,30 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
         <v>2400</v>
-      </c>
-      <c r="L57" s="3">
-        <v>50600</v>
       </c>
       <c r="M57" s="3">
         <v>50600</v>
       </c>
       <c r="N57" s="3">
+        <v>50600</v>
+      </c>
+      <c r="O57" s="3">
         <v>10000</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2728,98 +2861,104 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>9900</v>
-      </c>
-      <c r="L58" s="3">
-        <v>9500</v>
       </c>
       <c r="M58" s="3">
         <v>9500</v>
       </c>
       <c r="N58" s="3">
+        <v>9500</v>
+      </c>
+      <c r="O58" s="3">
         <v>6200</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E59" s="3">
         <v>5900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>27300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>62000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>18100</v>
       </c>
       <c r="M59" s="3">
         <v>18100</v>
       </c>
       <c r="N59" s="3">
+        <v>18100</v>
+      </c>
+      <c r="O59" s="3">
         <v>69100</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E60" s="3">
         <v>12800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>25200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>37400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>41100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>29300</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2835,9 +2974,12 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2866,50 +3008,53 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="M61" s="3">
         <v>1100</v>
       </c>
       <c r="N61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O61" s="3">
         <v>1400</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E62" s="3">
         <v>18000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>32600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>28900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>22000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13200</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -2925,9 +3070,12 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E66" s="3">
         <v>30700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>27300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>65500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>66300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>63100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>38400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>42500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>78600</v>
-      </c>
-      <c r="L66" s="3">
-        <v>87600</v>
       </c>
       <c r="M66" s="3">
         <v>87600</v>
       </c>
       <c r="N66" s="3">
+        <v>87600</v>
+      </c>
+      <c r="O66" s="3">
         <v>93300</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,44 +3474,47 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E72" s="3">
         <v>48200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>68400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>13600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-39900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7300</v>
-      </c>
-      <c r="L72" s="3">
-        <v>2100</v>
       </c>
       <c r="M72" s="3">
         <v>2100</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
+      <c r="N72" s="3">
+        <v>2100</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
@@ -3349,9 +3522,12 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>892700</v>
+      </c>
+      <c r="E76" s="3">
         <v>907000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>890200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>937100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>898900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>896400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>866200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>918100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>874000</v>
-      </c>
-      <c r="L76" s="3">
-        <v>749200</v>
       </c>
       <c r="M76" s="3">
         <v>749200</v>
       </c>
       <c r="N76" s="3">
+        <v>749200</v>
+      </c>
+      <c r="O76" s="3">
         <v>495400</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E81" s="3">
         <v>37500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-48900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>59200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>18800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>39200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-58100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>26800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7500</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,8 +3886,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3698,17 +3896,17 @@
         <v>400</v>
       </c>
       <c r="E83" s="3">
+        <v>400</v>
+      </c>
+      <c r="F83" s="3">
         <v>300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
@@ -3718,24 +3916,27 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E89" s="3">
         <v>145100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-70600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>238200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-279400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-44300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>77000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-67600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6600</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-58600</v>
       </c>
       <c r="M89" s="3">
         <v>-58600</v>
       </c>
       <c r="N89" s="3">
+        <v>-58600</v>
+      </c>
+      <c r="O89" s="3">
         <v>40800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2800</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,8 +4242,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4037,15 +4257,15 @@
       <c r="F91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3">
         <v>-11100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6500</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4061,15 +4281,18 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E94" s="3">
         <v>5800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>65300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-174100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4100</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>29400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1900</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,38 +4454,39 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E96" s="3">
         <v>4300</v>
-      </c>
-      <c r="E96" s="3">
-        <v>4400</v>
       </c>
       <c r="F96" s="3">
         <v>4400</v>
       </c>
       <c r="G96" s="3">
+        <v>4400</v>
+      </c>
+      <c r="H96" s="3">
         <v>6700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>4500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>4700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>4800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2500</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,54 +4643,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-59200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-25000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-37200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-14400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>150900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>34700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>65400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>105900</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>-50500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-88400</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4473,17 +4721,17 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -4491,52 +4739,58 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="E102" s="3">
         <v>125800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-107300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>289100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-302500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-61000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>116400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-21000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>108300</v>
-      </c>
-      <c r="L102" s="3">
-        <v>86000</v>
       </c>
       <c r="M102" s="3">
         <v>86000</v>
       </c>
       <c r="N102" s="3">
+        <v>86000</v>
+      </c>
+      <c r="O102" s="3">
         <v>19700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-89300</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
